--- a/results/soae/SOAE Results (rho=1.0, Flattop, BW=100Hz, Mode=phi)/SOAE N_xi Fitted Parameters (rho=1.0, Flattop, BW=100Hz, Mode=phi).xlsx
+++ b/results/soae/SOAE Results (rho=1.0, Flattop, BW=100Hz, Mode=phi)/SOAE N_xi Fitted Parameters (rho=1.0, Flattop, BW=100Hz, Mode=phi).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,45 +451,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Frequency (Rounded)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>N_xi</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>N_xi_std</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>T_xi</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>T_xi_std</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>A_xi</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>A_xi_std</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Decayed Xi</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Decayed Num Cycles</t>
         </is>
@@ -513,30 +518,33 @@
         <v>1235.467529296875</v>
       </c>
       <c r="E2" t="n">
+        <v>1235</v>
+      </c>
+      <c r="F2" t="n">
         <v>17.13201500261447</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.1890828434636662</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>0.01386682741258654</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>0.0001530455790863855</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>1.097098516875782</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>0.01326181442206069</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>5.704680377915166e-05</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.03700680272108844</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>45.720703125</v>
       </c>
     </row>
@@ -558,30 +566,33 @@
         <v>2153.3203125</v>
       </c>
       <c r="E3" t="n">
+        <v>2153</v>
+      </c>
+      <c r="F3" t="n">
         <v>21.525649488348</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.2684133580468332</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>0.009996492097990183</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>0.0001246509200181212</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>1.170114559792253</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>0.01624039480268145</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>5.966876490755497e-05</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.02800453514739229</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>60.302734375</v>
       </c>
     </row>
@@ -603,30 +614,33 @@
         <v>3703.7109375</v>
       </c>
       <c r="E4" t="n">
+        <v>3704</v>
+      </c>
+      <c r="F4" t="n">
         <v>33.09600746478618</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.8437673862921345</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>0.00893590456255367</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>0.0002278167493442878</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>1.247661513569817</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>0.03356443180539684</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>0.0002506046663234713</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.02299319727891156</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>85.16015625</v>
       </c>
     </row>
@@ -648,30 +662,33 @@
         <v>4500.439453125</v>
       </c>
       <c r="E5" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F5" t="n">
         <v>26.65002363601777</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.4572998801454387</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>0.005921649188617039</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>0.0001016122725143875</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.9787075623482409</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>0.02451301620026842</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>1.838194375009106e-05</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.01800453514739229</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>81.0283203125</v>
       </c>
     </row>
@@ -693,30 +710,33 @@
         <v>966.302490234375</v>
       </c>
       <c r="E6" t="n">
+        <v>966</v>
+      </c>
+      <c r="F6" t="n">
         <v>9.738286129994378</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.2259593524333384</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>0.01007788578463911</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>0.0002338391494557076</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.8443787316474445</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>0.0248362786822276</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>6.222616177053476e-05</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.02700680272108844</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>26.09674072265625</v>
       </c>
     </row>
@@ -735,34 +755,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3022.723388671875</v>
+        <v>3151.922607421875</v>
       </c>
       <c r="E7" t="n">
-        <v>32.54372184546421</v>
+        <v>3152</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8456363822285479</v>
+        <v>23.62249219195285</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0107663579034148</v>
+        <v>0.7471992794030228</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002797597641245314</v>
+        <v>0.007494629511628443</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5897221906560058</v>
+        <v>0.00023706142963142</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02276203901579016</v>
+        <v>1.184597386226075</v>
       </c>
       <c r="K7" t="n">
-        <v>2.540174760775601e-05</v>
+        <v>0.04287427192685948</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03099773242630385</v>
+        <v>0.0002320834512134212</v>
       </c>
       <c r="M7" t="n">
-        <v>93.69757080078125</v>
+        <v>0.02</v>
+      </c>
+      <c r="N7" t="n">
+        <v>63.0384521484375</v>
       </c>
     </row>
     <row r="8">
@@ -780,34 +803,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3151.922607421875</v>
+        <v>3954.034423828125</v>
       </c>
       <c r="E8" t="n">
-        <v>23.62249219195285</v>
+        <v>3954</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7471992794030228</v>
+        <v>20.8939729558373</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007494629511628443</v>
+        <v>0.978272918850697</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00023706142963142</v>
+        <v>0.005284216250097454</v>
       </c>
       <c r="I8" t="n">
-        <v>1.184597386226075</v>
+        <v>0.0002474113308056573</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04287427192685948</v>
+        <v>1.084334177567386</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002320834512134212</v>
+        <v>0.06058213478056951</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02</v>
+        <v>0.0002290086284680582</v>
       </c>
       <c r="M8" t="n">
-        <v>63.0384521484375</v>
+        <v>0.01399092970521542</v>
+      </c>
+      <c r="N8" t="n">
+        <v>55.32061767578125</v>
       </c>
     </row>
     <row r="9">
@@ -817,42 +843,45 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ACsb4rearSOAEwf1.mat</t>
+          <t>ACsb24rearSOAEwfA1.mat</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3954.034423828125</v>
+        <v>2177.545166015625</v>
       </c>
       <c r="E9" t="n">
-        <v>20.8939729558373</v>
+        <v>2178</v>
       </c>
       <c r="F9" t="n">
-        <v>0.978272918850697</v>
+        <v>24.48573524347724</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005284216250097454</v>
+        <v>0.5927101591342311</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0002474113308056573</v>
+        <v>0.01124465091499348</v>
       </c>
       <c r="I9" t="n">
-        <v>1.084334177567386</v>
+        <v>0.0002721919014055381</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06058213478056951</v>
+        <v>1.314019044375019</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0002290086284680582</v>
+        <v>0.03296218303069015</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01399092970521542</v>
+        <v>0.0003224398247706441</v>
       </c>
       <c r="M9" t="n">
-        <v>55.32061767578125</v>
+        <v>0.02800453514739229</v>
+      </c>
+      <c r="N9" t="n">
+        <v>60.98114013671875</v>
       </c>
     </row>
     <row r="10">
@@ -870,34 +899,37 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1811.480712890625</v>
+        <v>3111.5478515625</v>
       </c>
       <c r="E10" t="n">
-        <v>22.95053934956924</v>
+        <v>3112</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5629275030129419</v>
+        <v>21.13366505624681</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01266949142005851</v>
+        <v>0.534066259027716</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0003107554493995492</v>
+        <v>0.006792010299836557</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4738142396901148</v>
+        <v>0.0001716400597083951</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01935830725787554</v>
+        <v>1.290794362239294</v>
       </c>
       <c r="K10" t="n">
-        <v>1.394675850127233e-05</v>
+        <v>0.03939851166007741</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04099773242630386</v>
+        <v>0.000143082871270245</v>
       </c>
       <c r="M10" t="n">
-        <v>74.2666015625</v>
+        <v>0.01900226757369615</v>
+      </c>
+      <c r="N10" t="n">
+        <v>59.12646484375</v>
       </c>
     </row>
     <row r="11">
@@ -915,34 +947,37 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2177.545166015625</v>
+        <v>3477.6123046875</v>
       </c>
       <c r="E11" t="n">
-        <v>24.48573524347724</v>
+        <v>3478</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5927101591342311</v>
+        <v>23.49709256739069</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01124465091499348</v>
+        <v>0.7478092931156189</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0002721919014055381</v>
+        <v>0.00675667397878676</v>
       </c>
       <c r="I11" t="n">
-        <v>1.314019044375019</v>
+        <v>0.0002150352677633562</v>
       </c>
       <c r="J11" t="n">
-        <v>0.03296218303069015</v>
+        <v>1.294504960029209</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0003224398247706441</v>
+        <v>0.0552043707945719</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02800453514739229</v>
+        <v>0.0001534459607769112</v>
       </c>
       <c r="M11" t="n">
-        <v>60.98114013671875</v>
+        <v>0.01900226757369615</v>
+      </c>
+      <c r="N11" t="n">
+        <v>66.08251953125</v>
       </c>
     </row>
     <row r="12">
@@ -952,42 +987,45 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ACsb24rearSOAEwfA1.mat</t>
+          <t>ACsb30learSOAEwfA2.mat</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3111.5478515625</v>
+        <v>1798.0224609375</v>
       </c>
       <c r="E12" t="n">
-        <v>21.13366505624681</v>
+        <v>1798</v>
       </c>
       <c r="F12" t="n">
-        <v>0.534066259027716</v>
+        <v>14.32658648572139</v>
       </c>
       <c r="G12" t="n">
-        <v>0.006792010299836557</v>
+        <v>0.3256299467865978</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0001716400597083951</v>
+        <v>0.007967968586027238</v>
       </c>
       <c r="I12" t="n">
-        <v>1.290794362239294</v>
+        <v>0.0001811044933314194</v>
       </c>
       <c r="J12" t="n">
-        <v>0.03939851166007741</v>
+        <v>1.068082823242711</v>
       </c>
       <c r="K12" t="n">
-        <v>0.000143082871270245</v>
+        <v>0.02723396640347786</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01900226757369615</v>
+        <v>0.0001206118280625474</v>
       </c>
       <c r="M12" t="n">
-        <v>59.12646484375</v>
+        <v>0.02199546485260771</v>
+      </c>
+      <c r="N12" t="n">
+        <v>39.54833984375</v>
       </c>
     </row>
     <row r="13">
@@ -997,42 +1035,45 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ACsb24rearSOAEwfA1.mat</t>
+          <t>ACsb30learSOAEwfA2.mat</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3477.6123046875</v>
+        <v>2139.862060546875</v>
       </c>
       <c r="E13" t="n">
-        <v>23.49709256739069</v>
+        <v>2140</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7478092931156189</v>
+        <v>8.822868983221635</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00675667397878676</v>
+        <v>0.3513913445167566</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0002150352677633562</v>
+        <v>0.004123101739075094</v>
       </c>
       <c r="I13" t="n">
-        <v>1.294504960029209</v>
+        <v>0.0001642121475937347</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0552043707945719</v>
+        <v>1.058961194876682</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0001534459607769112</v>
+        <v>0.06692821581822565</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01900226757369615</v>
+        <v>4.032594323920266e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>66.08251953125</v>
+        <v>0.01199546485260771</v>
+      </c>
+      <c r="N13" t="n">
+        <v>25.66864013671875</v>
       </c>
     </row>
     <row r="14">
@@ -1050,34 +1091,37 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1798.0224609375</v>
+        <v>2417.10205078125</v>
       </c>
       <c r="E14" t="n">
-        <v>14.32658648572139</v>
+        <v>2417</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3256299467865978</v>
+        <v>10.08603369248246</v>
       </c>
       <c r="G14" t="n">
-        <v>0.007967968586027238</v>
+        <v>0.4371802799139968</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0001811044933314194</v>
+        <v>0.004172779419562561</v>
       </c>
       <c r="I14" t="n">
-        <v>1.068082823242711</v>
+        <v>0.0001808695995159544</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02723396640347786</v>
+        <v>0.9463009793141544</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0001206118280625474</v>
+        <v>0.06548964315901262</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02199546485260771</v>
+        <v>4.819299939459773e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>39.54833984375</v>
+        <v>0.01299319727891157</v>
+      </c>
+      <c r="N14" t="n">
+        <v>31.4058837890625</v>
       </c>
     </row>
     <row r="15">
@@ -1095,124 +1139,133 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2139.862060546875</v>
+        <v>2783.16650390625</v>
       </c>
       <c r="E15" t="n">
-        <v>8.822868983221635</v>
+        <v>2783</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3513913445167566</v>
+        <v>12.49585036063949</v>
       </c>
       <c r="G15" t="n">
-        <v>0.004123101739075094</v>
+        <v>0.6895755528962817</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0001642121475937347</v>
+        <v>0.004489796188298914</v>
       </c>
       <c r="I15" t="n">
-        <v>1.058961194876682</v>
+        <v>0.0002477665464600999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.06692821581822565</v>
+        <v>0.7189093325820786</v>
       </c>
       <c r="K15" t="n">
-        <v>4.032594323920266e-05</v>
+        <v>0.05133580676549751</v>
       </c>
       <c r="L15" t="n">
+        <v>8.145063180417934e-05</v>
+      </c>
+      <c r="M15" t="n">
         <v>0.01199546485260771</v>
       </c>
-      <c r="M15" t="n">
-        <v>25.66864013671875</v>
+      <c r="N15" t="n">
+        <v>33.3853759765625</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Anole</t>
+          <t>Tokay</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ACsb30learSOAEwfA2.mat</t>
+          <t>tokay_GG1rearSOAEwf.mat</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2417.10205078125</v>
+        <v>1342.7734375</v>
       </c>
       <c r="E16" t="n">
-        <v>10.08603369248246</v>
+        <v>1343</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4371802799139968</v>
+        <v>6.142486686914508</v>
       </c>
       <c r="G16" t="n">
-        <v>0.004172779419562561</v>
+        <v>0.257729026237118</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0001808695995159544</v>
+        <v>0.004574477358109424</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9463009793141544</v>
+        <v>0.0001919378348122246</v>
       </c>
       <c r="J16" t="n">
-        <v>0.06548964315901262</v>
+        <v>1.055792527495161</v>
       </c>
       <c r="K16" t="n">
-        <v>4.819299939459773e-05</v>
+        <v>0.07744037082427963</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01299319727891157</v>
+        <v>6.465119898194724e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>31.4058837890625</v>
+        <v>0.017</v>
+      </c>
+      <c r="N16" t="n">
+        <v>22.8271484375</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Anole</t>
+          <t>Tokay</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ACsb30learSOAEwfA2.mat</t>
+          <t>tokay_GG1rearSOAEwf.mat</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2783.16650390625</v>
+        <v>1779.1748046875</v>
       </c>
       <c r="E17" t="n">
-        <v>12.49585036063949</v>
+        <v>1779</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6895755528962817</v>
+        <v>12.39925854007714</v>
       </c>
       <c r="G17" t="n">
-        <v>0.004489796188298914</v>
+        <v>0.2582283723861958</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0002477665464600999</v>
+        <v>0.006969106412371316</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7189093325820786</v>
+        <v>0.0001451394049116786</v>
       </c>
       <c r="J17" t="n">
-        <v>0.05133580676549751</v>
+        <v>1.012954998959984</v>
       </c>
       <c r="K17" t="n">
-        <v>8.145063180417934e-05</v>
+        <v>0.03393058302949695</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01199546485260771</v>
+        <v>2.825360334462931e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>33.3853759765625</v>
+        <v>0.023</v>
+      </c>
+      <c r="N17" t="n">
+        <v>40.92102050781249</v>
       </c>
     </row>
     <row r="18">
@@ -1230,34 +1283,37 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1342.7734375</v>
+        <v>3649.90234375</v>
       </c>
       <c r="E18" t="n">
-        <v>6.142486686914508</v>
+        <v>3650</v>
       </c>
       <c r="F18" t="n">
-        <v>0.257729026237118</v>
+        <v>22.28436400937938</v>
       </c>
       <c r="G18" t="n">
-        <v>0.004574477358109424</v>
+        <v>0.7142278398670143</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0001919378348122246</v>
+        <v>0.006105468560696854</v>
       </c>
       <c r="I18" t="n">
-        <v>1.055792527495161</v>
+        <v>0.0001956840957923271</v>
       </c>
       <c r="J18" t="n">
-        <v>0.07744037082427963</v>
+        <v>0.7452506893430624</v>
       </c>
       <c r="K18" t="n">
-        <v>6.465119898194724e-05</v>
+        <v>0.03066526312090223</v>
       </c>
       <c r="L18" t="n">
-        <v>0.017</v>
+        <v>6.021384322250267e-05</v>
       </c>
       <c r="M18" t="n">
-        <v>22.8271484375</v>
+        <v>0.018</v>
+      </c>
+      <c r="N18" t="n">
+        <v>65.69824218749999</v>
       </c>
     </row>
     <row r="19">
@@ -1275,34 +1331,37 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1779.1748046875</v>
+        <v>4211.425781249999</v>
       </c>
       <c r="E19" t="n">
-        <v>12.39925854007714</v>
+        <v>4211</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2582283723861958</v>
+        <v>40.37939601622071</v>
       </c>
       <c r="G19" t="n">
-        <v>0.006969106412371316</v>
+        <v>0.5028590038015661</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0001451394049116786</v>
+        <v>0.009588058323619714</v>
       </c>
       <c r="I19" t="n">
-        <v>1.012954998959984</v>
+        <v>0.0001194035060620994</v>
       </c>
       <c r="J19" t="n">
-        <v>0.03393058302949695</v>
+        <v>0.9341567441682173</v>
       </c>
       <c r="K19" t="n">
-        <v>2.825360334462931e-05</v>
+        <v>0.01545843710960675</v>
       </c>
       <c r="L19" t="n">
-        <v>0.023</v>
+        <v>2.269715053667822e-05</v>
       </c>
       <c r="M19" t="n">
-        <v>40.92102050781249</v>
+        <v>0.029</v>
+      </c>
+      <c r="N19" t="n">
+        <v>122.13134765625</v>
       </c>
     </row>
     <row r="20">
@@ -1312,42 +1371,45 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>tokay_GG1rearSOAEwf.mat</t>
+          <t>tokay_GG2rearSOAEwf.mat</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3649.90234375</v>
+        <v>1364.1357421875</v>
       </c>
       <c r="E20" t="n">
-        <v>22.28436400937938</v>
+        <v>1364</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7142278398670143</v>
+        <v>6.796755403452015</v>
       </c>
       <c r="G20" t="n">
-        <v>0.006105468560696854</v>
+        <v>0.1623968588960492</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0001956840957923271</v>
+        <v>0.004982462663541737</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7452506893430624</v>
+        <v>0.0001190474333849159</v>
       </c>
       <c r="J20" t="n">
-        <v>0.03066526312090223</v>
+        <v>0.7682611542344919</v>
       </c>
       <c r="K20" t="n">
-        <v>6.021384322250267e-05</v>
+        <v>0.0336970045900381</v>
       </c>
       <c r="L20" t="n">
+        <v>9.240797155417901e-06</v>
+      </c>
+      <c r="M20" t="n">
         <v>0.018</v>
       </c>
-      <c r="M20" t="n">
-        <v>65.69824218749999</v>
+      <c r="N20" t="n">
+        <v>24.55444335937499</v>
       </c>
     </row>
     <row r="21">
@@ -1357,42 +1419,45 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>tokay_GG1rearSOAEwf.mat</t>
+          <t>tokay_GG2rearSOAEwf.mat</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4211.425781249999</v>
+        <v>1776.123046875</v>
       </c>
       <c r="E21" t="n">
-        <v>40.37939601622071</v>
+        <v>1776</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5028590038015661</v>
+        <v>10.26799158872613</v>
       </c>
       <c r="G21" t="n">
-        <v>0.009588058323619714</v>
+        <v>0.1607119400006531</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0001194035060620994</v>
+        <v>0.005781126260814051</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9341567441682173</v>
+        <v>9.048468814332306e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.01545843710960675</v>
+        <v>0.7338593687726034</v>
       </c>
       <c r="K21" t="n">
-        <v>2.269715053667822e-05</v>
+        <v>0.01879930361204938</v>
       </c>
       <c r="L21" t="n">
-        <v>0.029</v>
+        <v>5.230551042633749e-06</v>
       </c>
       <c r="M21" t="n">
-        <v>122.13134765625</v>
+        <v>0.018</v>
+      </c>
+      <c r="N21" t="n">
+        <v>31.97021484374999</v>
       </c>
     </row>
     <row r="22">
@@ -1410,34 +1475,37 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1364.1357421875</v>
+        <v>3607.177734375</v>
       </c>
       <c r="E22" t="n">
-        <v>6.796755403452015</v>
+        <v>3607</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1623968588960492</v>
+        <v>26.15056639772489</v>
       </c>
       <c r="G22" t="n">
-        <v>0.004982462663541737</v>
+        <v>0.6232386462167635</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0001190474333849159</v>
+        <v>0.007249591875809215</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7682611542344919</v>
+        <v>0.0001727773600611752</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0336970045900381</v>
+        <v>1.055367179637779</v>
       </c>
       <c r="K22" t="n">
-        <v>9.240797155417901e-06</v>
+        <v>0.03266490931419948</v>
       </c>
       <c r="L22" t="n">
-        <v>0.018</v>
+        <v>7.605522370861679e-05</v>
       </c>
       <c r="M22" t="n">
-        <v>24.55444335937499</v>
+        <v>0.021</v>
+      </c>
+      <c r="N22" t="n">
+        <v>75.750732421875</v>
       </c>
     </row>
     <row r="23">
@@ -1455,34 +1523,37 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1776.123046875</v>
+        <v>4394.531249999999</v>
       </c>
       <c r="E23" t="n">
-        <v>10.26799158872613</v>
+        <v>4395</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1607119400006531</v>
+        <v>25.28556872677591</v>
       </c>
       <c r="G23" t="n">
-        <v>0.005781126260814051</v>
+        <v>1.345214932115085</v>
       </c>
       <c r="H23" t="n">
-        <v>9.048468814332306e-05</v>
+        <v>0.005753871639159676</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7338593687726034</v>
+        <v>0.0003061111312190772</v>
       </c>
       <c r="J23" t="n">
-        <v>0.01879930361204938</v>
+        <v>0.7188573874888537</v>
       </c>
       <c r="K23" t="n">
-        <v>5.230551042633749e-06</v>
+        <v>0.05004770801948433</v>
       </c>
       <c r="L23" t="n">
-        <v>0.018</v>
+        <v>0.0001150108058476167</v>
       </c>
       <c r="M23" t="n">
-        <v>31.97021484374999</v>
+        <v>0.016</v>
+      </c>
+      <c r="N23" t="n">
+        <v>70.31249999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1492,42 +1563,45 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>tokay_GG2rearSOAEwf.mat</t>
+          <t>tokay_GG3rearSOAEwf.mat</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3607.177734375</v>
+        <v>1257.32421875</v>
       </c>
       <c r="E24" t="n">
-        <v>26.15056639772489</v>
+        <v>1257</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6232386462167635</v>
+        <v>12.14179487862508</v>
       </c>
       <c r="G24" t="n">
-        <v>0.007249591875809215</v>
+        <v>0.1248147911735354</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0001727773600611752</v>
+        <v>0.009656852781135603</v>
       </c>
       <c r="I24" t="n">
-        <v>1.055367179637779</v>
+        <v>9.927017177607789e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.03266490931419948</v>
+        <v>0.6930263207003368</v>
       </c>
       <c r="K24" t="n">
-        <v>7.605522370861679e-05</v>
+        <v>0.008537000735201875</v>
       </c>
       <c r="L24" t="n">
-        <v>0.021</v>
+        <v>8.913687039553479e-06</v>
       </c>
       <c r="M24" t="n">
-        <v>75.750732421875</v>
+        <v>0.025</v>
+      </c>
+      <c r="N24" t="n">
+        <v>31.43310546875</v>
       </c>
     </row>
     <row r="25">
@@ -1537,42 +1611,45 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>tokay_GG2rearSOAEwf.mat</t>
+          <t>tokay_GG3rearSOAEwf.mat</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4394.531249999999</v>
+        <v>2578.7353515625</v>
       </c>
       <c r="E25" t="n">
-        <v>25.28556872677591</v>
+        <v>2579</v>
       </c>
       <c r="F25" t="n">
-        <v>1.345214932115085</v>
+        <v>10.36106920468176</v>
       </c>
       <c r="G25" t="n">
-        <v>0.005753871639159676</v>
+        <v>0.5985495421290785</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0003061111312190772</v>
+        <v>0.004017887759751622</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7188573874888537</v>
+        <v>0.0002321097206684692</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05004770801948433</v>
+        <v>1.08825852345189</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0001150108058476167</v>
+        <v>0.1185960827141798</v>
       </c>
       <c r="L25" t="n">
-        <v>0.016</v>
+        <v>6.294231525518859e-05</v>
       </c>
       <c r="M25" t="n">
-        <v>70.31249999999999</v>
+        <v>0.014</v>
+      </c>
+      <c r="N25" t="n">
+        <v>36.10229492187499</v>
       </c>
     </row>
     <row r="26">
@@ -1590,34 +1667,37 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1257.32421875</v>
+        <v>3567.5048828125</v>
       </c>
       <c r="E26" t="n">
-        <v>12.14179487862508</v>
+        <v>3568</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1248147911735354</v>
+        <v>24.55895048303828</v>
       </c>
       <c r="G26" t="n">
-        <v>0.009656852781135603</v>
+        <v>0.5780208668700074</v>
       </c>
       <c r="H26" t="n">
-        <v>9.927017177607789e-05</v>
+        <v>0.006884069199556873</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6930263207003368</v>
+        <v>0.0001620238474388059</v>
       </c>
       <c r="J26" t="n">
-        <v>0.008537000735201875</v>
+        <v>0.9917107085443441</v>
       </c>
       <c r="K26" t="n">
-        <v>8.913687039553479e-06</v>
+        <v>0.03114340540663109</v>
       </c>
       <c r="L26" t="n">
-        <v>0.025</v>
+        <v>5.572152607044267e-05</v>
       </c>
       <c r="M26" t="n">
-        <v>31.43310546875</v>
+        <v>0.02</v>
+      </c>
+      <c r="N26" t="n">
+        <v>71.35009765624999</v>
       </c>
     </row>
     <row r="27">
@@ -1627,42 +1707,45 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>tokay_GG3rearSOAEwf.mat</t>
+          <t>tokay_GG4rearSOAEwf.mat</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1837.158203125</v>
+        <v>1251.220703125</v>
       </c>
       <c r="E27" t="n">
-        <v>8.436579553308851</v>
+        <v>1251</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6831694383902649</v>
+        <v>11.4289298842233</v>
       </c>
       <c r="G27" t="n">
-        <v>0.004592190013335955</v>
+        <v>0.2244084512645322</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0003718620624114984</v>
+        <v>0.009134223766981196</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7074261131487773</v>
+        <v>0.0001793516129521023</v>
       </c>
       <c r="J27" t="n">
-        <v>0.08619062723623604</v>
+        <v>0.8292617934162849</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0001338669915275768</v>
+        <v>0.0204230059907636</v>
       </c>
       <c r="L27" t="n">
-        <v>0.014</v>
+        <v>4.59877167889005e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>25.72021484375</v>
+        <v>0.026</v>
+      </c>
+      <c r="N27" t="n">
+        <v>32.53173828124999</v>
       </c>
     </row>
     <row r="28">
@@ -1672,42 +1755,45 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>tokay_GG3rearSOAEwf.mat</t>
+          <t>tokay_GG4rearSOAEwf.mat</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2578.7353515625</v>
+        <v>2590.9423828125</v>
       </c>
       <c r="E28" t="n">
-        <v>10.36106920468176</v>
+        <v>2591</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5985495421290785</v>
+        <v>16.06611415089595</v>
       </c>
       <c r="G28" t="n">
-        <v>0.004017887759751622</v>
+        <v>0.687192293862055</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0002321097206684692</v>
+        <v>0.006200876660736848</v>
       </c>
       <c r="I28" t="n">
-        <v>1.08825852345189</v>
+        <v>0.0002652287053624479</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1185960827141798</v>
+        <v>0.9792491006494375</v>
       </c>
       <c r="K28" t="n">
-        <v>6.294231525518859e-05</v>
+        <v>0.0596288887123586</v>
       </c>
       <c r="L28" t="n">
-        <v>0.014</v>
+        <v>0.0001373910199579619</v>
       </c>
       <c r="M28" t="n">
-        <v>36.10229492187499</v>
+        <v>0.019</v>
+      </c>
+      <c r="N28" t="n">
+        <v>49.22790527343749</v>
       </c>
     </row>
     <row r="29">
@@ -1717,42 +1803,45 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>tokay_GG3rearSOAEwf.mat</t>
+          <t>tokay_GG4rearSOAEwf.mat</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3567.5048828125</v>
+        <v>3216.552734375</v>
       </c>
       <c r="E29" t="n">
-        <v>24.55895048303828</v>
+        <v>3217</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5780208668700074</v>
+        <v>18.25537526981401</v>
       </c>
       <c r="G29" t="n">
-        <v>0.006884069199556873</v>
+        <v>0.8444671924882021</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0001620238474388059</v>
+        <v>0.005675447218607833</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9917107085443441</v>
+        <v>0.0002625379598050608</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03114340540663109</v>
+        <v>0.6914529911217143</v>
       </c>
       <c r="K29" t="n">
-        <v>5.572152607044267e-05</v>
+        <v>0.04273524415684581</v>
       </c>
       <c r="L29" t="n">
-        <v>0.02</v>
+        <v>8.759899053303481e-05</v>
       </c>
       <c r="M29" t="n">
-        <v>71.35009765624999</v>
+        <v>0.017</v>
+      </c>
+      <c r="N29" t="n">
+        <v>54.68139648437499</v>
       </c>
     </row>
     <row r="30">
@@ -1770,169 +1859,181 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1251.220703125</v>
+        <v>3582.763671875</v>
       </c>
       <c r="E30" t="n">
-        <v>11.4289298842233</v>
+        <v>3583</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2244084512645322</v>
+        <v>22.5808485294681</v>
       </c>
       <c r="G30" t="n">
-        <v>0.009134223766981196</v>
+        <v>0.7393287462016108</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0001793516129521023</v>
+        <v>0.006302634110848474</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8292617934162849</v>
+        <v>0.0002063571069466302</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0204230059907636</v>
+        <v>0.8310339547185269</v>
       </c>
       <c r="K30" t="n">
-        <v>4.59877167889005e-05</v>
+        <v>0.03016188684557085</v>
       </c>
       <c r="L30" t="n">
-        <v>0.026</v>
+        <v>0.0001126747153798341</v>
       </c>
       <c r="M30" t="n">
-        <v>32.53173828124999</v>
+        <v>0.017</v>
+      </c>
+      <c r="N30" t="n">
+        <v>60.906982421875</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tokay</t>
+          <t>Owl</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>tokay_GG4rearSOAEwf.mat</t>
+          <t>Owl2R1.mat</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2590.9423828125</v>
+        <v>4350.5859375</v>
       </c>
       <c r="E31" t="n">
-        <v>16.06611415089595</v>
+        <v>4351</v>
       </c>
       <c r="F31" t="n">
-        <v>0.687192293862055</v>
+        <v>20.67471268169182</v>
       </c>
       <c r="G31" t="n">
-        <v>0.006200876660736848</v>
+        <v>2.198486909544176</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0002652287053624479</v>
+        <v>0.004752167404276638</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9792491006494375</v>
+        <v>0.0005053312223060014</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0596288887123586</v>
+        <v>0.5628985668153356</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0001373910199579619</v>
+        <v>0.07434436510945416</v>
       </c>
       <c r="L31" t="n">
-        <v>0.019</v>
+        <v>0.0001984464489565307</v>
       </c>
       <c r="M31" t="n">
-        <v>49.22790527343749</v>
+        <v>0.012</v>
+      </c>
+      <c r="N31" t="n">
+        <v>52.20703125</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tokay</t>
+          <t>Owl</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>tokay_GG4rearSOAEwf.mat</t>
+          <t>Owl2R1.mat</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3216.552734375</v>
+        <v>7453.125</v>
       </c>
       <c r="E32" t="n">
-        <v>18.25537526981401</v>
+        <v>7453</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8444671924882021</v>
+        <v>33.08770262631539</v>
       </c>
       <c r="G32" t="n">
-        <v>0.005675447218607833</v>
+        <v>1.630907799118644</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0002625379598050608</v>
+        <v>0.004439440184662862</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6914529911217143</v>
+        <v>0.0002188220107832143</v>
       </c>
       <c r="J32" t="n">
-        <v>0.04273524415684581</v>
+        <v>0.8864300467824728</v>
       </c>
       <c r="K32" t="n">
-        <v>8.759899053303481e-05</v>
+        <v>0.06742047804351127</v>
       </c>
       <c r="L32" t="n">
-        <v>0.017</v>
+        <v>7.274329691944462e-05</v>
       </c>
       <c r="M32" t="n">
-        <v>54.68139648437499</v>
+        <v>0.014</v>
+      </c>
+      <c r="N32" t="n">
+        <v>104.34375</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tokay</t>
+          <t>Owl</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>tokay_GG4rearSOAEwf.mat</t>
+          <t>Owl2R1.mat</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3582.763671875</v>
+        <v>8452.1484375</v>
       </c>
       <c r="E33" t="n">
-        <v>22.5808485294681</v>
+        <v>8452</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7393287462016108</v>
+        <v>39.86614357346141</v>
       </c>
       <c r="G33" t="n">
-        <v>0.006302634110848474</v>
+        <v>2.118395738344804</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0002063571069466302</v>
+        <v>0.004716687581655053</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8310339547185269</v>
+        <v>0.0002506339960791541</v>
       </c>
       <c r="J33" t="n">
-        <v>0.03016188684557085</v>
+        <v>0.8162419191893981</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0001126747153798341</v>
+        <v>0.04654587706699751</v>
       </c>
       <c r="L33" t="n">
-        <v>0.017</v>
+        <v>0.0001885685597666911</v>
       </c>
       <c r="M33" t="n">
-        <v>60.906982421875</v>
+        <v>0.012</v>
+      </c>
+      <c r="N33" t="n">
+        <v>101.42578125</v>
       </c>
     </row>
     <row r="34">
@@ -1950,34 +2051,37 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4350.5859375</v>
+        <v>9026.3671875</v>
       </c>
       <c r="E34" t="n">
-        <v>20.67471268169182</v>
+        <v>9026</v>
       </c>
       <c r="F34" t="n">
-        <v>2.198486909544176</v>
+        <v>50.3142592938533</v>
       </c>
       <c r="G34" t="n">
-        <v>0.004752167404276638</v>
+        <v>1.888111171225259</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0005053312223060014</v>
+        <v>0.005574142758509768</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5628985668153356</v>
+        <v>0.0002091773059974754</v>
       </c>
       <c r="J34" t="n">
-        <v>0.07434436510945416</v>
+        <v>0.8928197164887637</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0001984464489565307</v>
+        <v>0.03855786706597979</v>
       </c>
       <c r="L34" t="n">
-        <v>0.012</v>
+        <v>0.0001056339563843901</v>
       </c>
       <c r="M34" t="n">
-        <v>52.20703125</v>
+        <v>0.014</v>
+      </c>
+      <c r="N34" t="n">
+        <v>126.369140625</v>
       </c>
     </row>
     <row r="35">
@@ -1987,42 +2091,45 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Owl2R1.mat</t>
+          <t>Owl7L1.mat</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>7453.125</v>
+        <v>6837.890625</v>
       </c>
       <c r="E35" t="n">
-        <v>33.08770262631539</v>
+        <v>6838</v>
       </c>
       <c r="F35" t="n">
-        <v>1.630907799118644</v>
+        <v>31.39472337683835</v>
       </c>
       <c r="G35" t="n">
-        <v>0.004439440184662862</v>
+        <v>1.528559038481109</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0002188220107832143</v>
+        <v>0.004591287737486786</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8864300467824728</v>
+        <v>0.0002235424814916675</v>
       </c>
       <c r="J35" t="n">
-        <v>0.06742047804351127</v>
+        <v>0.7774309696065362</v>
       </c>
       <c r="K35" t="n">
-        <v>7.274329691944462e-05</v>
+        <v>0.05614587682658816</v>
       </c>
       <c r="L35" t="n">
-        <v>0.014</v>
+        <v>4.91200374438796e-05</v>
       </c>
       <c r="M35" t="n">
-        <v>104.34375</v>
+        <v>0.013</v>
+      </c>
+      <c r="N35" t="n">
+        <v>88.892578125</v>
       </c>
     </row>
     <row r="36">
@@ -2032,42 +2139,45 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Owl2R1.mat</t>
+          <t>Owl7L1.mat</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8452.1484375</v>
+        <v>7901.3671875</v>
       </c>
       <c r="E36" t="n">
-        <v>39.86614357346141</v>
+        <v>7901</v>
       </c>
       <c r="F36" t="n">
-        <v>2.118395738344804</v>
+        <v>42.30790937607152</v>
       </c>
       <c r="G36" t="n">
-        <v>0.004716687581655053</v>
+        <v>1.710852358293182</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0002506339960791541</v>
+        <v>0.005354504906822054</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8162419191893981</v>
+        <v>0.0002165261172774958</v>
       </c>
       <c r="J36" t="n">
-        <v>0.04654587706699751</v>
+        <v>0.930502201984459</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0001885685597666911</v>
+        <v>0.05181871232466971</v>
       </c>
       <c r="L36" t="n">
-        <v>0.012</v>
+        <v>9.908266992408581e-05</v>
       </c>
       <c r="M36" t="n">
-        <v>101.42578125</v>
+        <v>0.016</v>
+      </c>
+      <c r="N36" t="n">
+        <v>126.421875</v>
       </c>
     </row>
     <row r="37">
@@ -2077,42 +2187,45 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Owl2R1.mat</t>
+          <t>Owl7L1.mat</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>9026.3671875</v>
+        <v>8835.9375</v>
       </c>
       <c r="E37" t="n">
-        <v>50.3142592938533</v>
+        <v>8836</v>
       </c>
       <c r="F37" t="n">
-        <v>1.888111171225259</v>
+        <v>42.28736802302278</v>
       </c>
       <c r="G37" t="n">
-        <v>0.005574142758509768</v>
+        <v>2.003185354445889</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0002091773059974754</v>
+        <v>0.00478583829084608</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8928197164887637</v>
+        <v>0.0002267088641636373</v>
       </c>
       <c r="J37" t="n">
-        <v>0.03855786706597979</v>
+        <v>1.072661207110922</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0001056339563843901</v>
+        <v>0.07412196398429062</v>
       </c>
       <c r="L37" t="n">
+        <v>0.0001138270765183201</v>
+      </c>
+      <c r="M37" t="n">
         <v>0.014</v>
       </c>
-      <c r="M37" t="n">
-        <v>126.369140625</v>
+      <c r="N37" t="n">
+        <v>123.703125</v>
       </c>
     </row>
     <row r="38">
@@ -2130,34 +2243,37 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6837.890625</v>
+        <v>9257.8125</v>
       </c>
       <c r="E38" t="n">
-        <v>31.39472337683835</v>
+        <v>9258</v>
       </c>
       <c r="F38" t="n">
-        <v>1.528559038481109</v>
+        <v>37.25734393967119</v>
       </c>
       <c r="G38" t="n">
-        <v>0.004591287737486786</v>
+        <v>1.05265036176258</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0002235424814916675</v>
+        <v>0.004024421961415959</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7774309696065362</v>
+        <v>0.0001137040053211901</v>
       </c>
       <c r="J38" t="n">
-        <v>0.05614587682658816</v>
+        <v>0.5875232116110591</v>
       </c>
       <c r="K38" t="n">
-        <v>4.91200374438796e-05</v>
+        <v>0.01895219466675426</v>
       </c>
       <c r="L38" t="n">
-        <v>0.013</v>
+        <v>1.596413307436488e-05</v>
       </c>
       <c r="M38" t="n">
-        <v>88.892578125</v>
+        <v>0.01</v>
+      </c>
+      <c r="N38" t="n">
+        <v>92.578125</v>
       </c>
     </row>
     <row r="39">
@@ -2167,42 +2283,45 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Owl7L1.mat</t>
+          <t>TAG6rearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>7901.3671875</v>
+        <v>5625.54931640625</v>
       </c>
       <c r="E39" t="n">
-        <v>42.30790937607152</v>
+        <v>5626</v>
       </c>
       <c r="F39" t="n">
-        <v>1.710852358293182</v>
+        <v>35.83188754427032</v>
       </c>
       <c r="G39" t="n">
-        <v>0.005354504906822054</v>
+        <v>0.9894803948067918</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0002165261172774958</v>
+        <v>0.006369491320566839</v>
       </c>
       <c r="I39" t="n">
-        <v>0.930502201984459</v>
+        <v>0.0001758904489417752</v>
       </c>
       <c r="J39" t="n">
-        <v>0.05181871232466971</v>
+        <v>0.7825726567811951</v>
       </c>
       <c r="K39" t="n">
-        <v>9.908266992408581e-05</v>
+        <v>0.02990582253091608</v>
       </c>
       <c r="L39" t="n">
-        <v>0.016</v>
+        <v>3.461679404252445e-05</v>
       </c>
       <c r="M39" t="n">
-        <v>126.421875</v>
+        <v>0.01800453514739229</v>
+      </c>
+      <c r="N39" t="n">
+        <v>101.285400390625</v>
       </c>
     </row>
     <row r="40">
@@ -2212,42 +2331,45 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Owl7L1.mat</t>
+          <t>TAG6rearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8835.9375</v>
+        <v>8096.484375</v>
       </c>
       <c r="E40" t="n">
-        <v>42.28736802302278</v>
+        <v>8096</v>
       </c>
       <c r="F40" t="n">
-        <v>2.003185354445889</v>
+        <v>44.17793082431302</v>
       </c>
       <c r="G40" t="n">
-        <v>0.00478583829084608</v>
+        <v>2.007478649265472</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0002267088641636373</v>
+        <v>0.005456433777692929</v>
       </c>
       <c r="I40" t="n">
-        <v>1.072661207110922</v>
+        <v>0.0002479444850735567</v>
       </c>
       <c r="J40" t="n">
-        <v>0.07412196398429062</v>
+        <v>0.7680204396392084</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0001138270765183201</v>
+        <v>0.04073507396957321</v>
       </c>
       <c r="L40" t="n">
-        <v>0.014</v>
+        <v>0.0001124669517117476</v>
       </c>
       <c r="M40" t="n">
-        <v>123.703125</v>
+        <v>0.01399092970521542</v>
+      </c>
+      <c r="N40" t="n">
+        <v>113.27734375</v>
       </c>
     </row>
     <row r="41">
@@ -2257,42 +2379,45 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Owl7L1.mat</t>
+          <t>TAG6rearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>9257.8125</v>
+        <v>8489.46533203125</v>
       </c>
       <c r="E41" t="n">
-        <v>37.25734393967119</v>
+        <v>8489</v>
       </c>
       <c r="F41" t="n">
-        <v>1.05265036176258</v>
+        <v>76.17464115123292</v>
       </c>
       <c r="G41" t="n">
-        <v>0.004024421961415959</v>
+        <v>1.303462049422885</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0001137040053211901</v>
+        <v>0.008972843185285359</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5875232116110591</v>
+        <v>0.0001535387681606811</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01895219466675426</v>
+        <v>0.9922119452824087</v>
       </c>
       <c r="K41" t="n">
-        <v>1.596413307436488e-05</v>
+        <v>0.01963014880734984</v>
       </c>
       <c r="L41" t="n">
-        <v>0.01</v>
+        <v>5.721431321694003e-05</v>
       </c>
       <c r="M41" t="n">
-        <v>92.578125</v>
+        <v>0.02399092970521542</v>
+      </c>
+      <c r="N41" t="n">
+        <v>203.670166015625</v>
       </c>
     </row>
     <row r="42">
@@ -2310,34 +2435,37 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>5625.54931640625</v>
+        <v>9864.898681640625</v>
       </c>
       <c r="E42" t="n">
-        <v>35.83188754427032</v>
+        <v>9865</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9894803948067918</v>
+        <v>53.46053663945462</v>
       </c>
       <c r="G42" t="n">
-        <v>0.006369491320566839</v>
+        <v>2.983201270209513</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0001758904489417752</v>
+        <v>0.005419268698516793</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7825726567811951</v>
+        <v>0.0003024056674562195</v>
       </c>
       <c r="J42" t="n">
-        <v>0.02990582253091608</v>
+        <v>0.7303670510474821</v>
       </c>
       <c r="K42" t="n">
-        <v>3.461679404252445e-05</v>
+        <v>0.04851252360364324</v>
       </c>
       <c r="L42" t="n">
-        <v>0.01800453514739229</v>
+        <v>0.0001724898735822209</v>
       </c>
       <c r="M42" t="n">
-        <v>101.285400390625</v>
+        <v>0.01501133786848073</v>
+      </c>
+      <c r="N42" t="n">
+        <v>148.0853271484375</v>
       </c>
     </row>
     <row r="43">
@@ -2347,42 +2475,45 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TAG6rearSOAEwf1.mat</t>
+          <t>owl_TAG4learSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>8096.484375</v>
+        <v>4944.561767578125</v>
       </c>
       <c r="E43" t="n">
-        <v>44.17793082431302</v>
+        <v>4945</v>
       </c>
       <c r="F43" t="n">
-        <v>2.007478649265472</v>
+        <v>22.03331658222185</v>
       </c>
       <c r="G43" t="n">
-        <v>0.005456433777692929</v>
+        <v>1.323424371734479</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0002479444850735567</v>
+        <v>0.004456070652549234</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7680204396392084</v>
+        <v>0.000267652510766935</v>
       </c>
       <c r="J43" t="n">
-        <v>0.04073507396957321</v>
+        <v>0.8390615718246441</v>
       </c>
       <c r="K43" t="n">
-        <v>0.0001124669517117476</v>
+        <v>0.07752962255165763</v>
       </c>
       <c r="L43" t="n">
+        <v>9.804808541461031e-05</v>
+      </c>
+      <c r="M43" t="n">
         <v>0.01399092970521542</v>
       </c>
-      <c r="M43" t="n">
-        <v>113.27734375</v>
+      <c r="N43" t="n">
+        <v>69.17901611328125</v>
       </c>
     </row>
     <row r="44">
@@ -2392,42 +2523,45 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TAG6rearSOAEwf1.mat</t>
+          <t>owl_TAG4learSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8489.46533203125</v>
+        <v>5768.206787109375</v>
       </c>
       <c r="E44" t="n">
-        <v>76.17464115123292</v>
+        <v>5768</v>
       </c>
       <c r="F44" t="n">
-        <v>1.303462049422885</v>
+        <v>53.45315335308301</v>
       </c>
       <c r="G44" t="n">
-        <v>0.008972843185285359</v>
+        <v>0.9190683849990305</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0001535387681606811</v>
+        <v>0.00926685802467044</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9922119452824087</v>
+        <v>0.0001593334668675434</v>
       </c>
       <c r="J44" t="n">
-        <v>0.01963014880734984</v>
+        <v>0.8631836995948721</v>
       </c>
       <c r="K44" t="n">
-        <v>5.721431321694003e-05</v>
+        <v>0.01707213762777284</v>
       </c>
       <c r="L44" t="n">
-        <v>0.02399092970521542</v>
+        <v>5.101002314508482e-05</v>
       </c>
       <c r="M44" t="n">
-        <v>203.670166015625</v>
+        <v>0.02600907029478458</v>
+      </c>
+      <c r="N44" t="n">
+        <v>150.0256958007812</v>
       </c>
     </row>
     <row r="45">
@@ -2437,42 +2571,45 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TAG6rearSOAEwf1.mat</t>
+          <t>owl_TAG4learSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>9864.898681640625</v>
+        <v>7184.014892578125</v>
       </c>
       <c r="E45" t="n">
-        <v>53.46053663945462</v>
+        <v>7184</v>
       </c>
       <c r="F45" t="n">
-        <v>2.983201270209513</v>
+        <v>212.2932172223761</v>
       </c>
       <c r="G45" t="n">
-        <v>0.005419268698516793</v>
+        <v>2.814804876179097</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0003024056674562195</v>
+        <v>0.02955077632727324</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7303670510474821</v>
+        <v>0.0003918150112811012</v>
       </c>
       <c r="J45" t="n">
-        <v>0.04851252360364324</v>
+        <v>1.191974460537603</v>
       </c>
       <c r="K45" t="n">
-        <v>0.0001724898735822209</v>
+        <v>0.01450831463645014</v>
       </c>
       <c r="L45" t="n">
-        <v>0.01501133786848073</v>
+        <v>0.0002984796442141717</v>
       </c>
       <c r="M45" t="n">
-        <v>148.0853271484375</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="N45" t="n">
+        <v>502.8810424804688</v>
       </c>
     </row>
     <row r="46">
@@ -2490,169 +2627,181 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4944.561767578125</v>
+        <v>9633.416748046875</v>
       </c>
       <c r="E46" t="n">
-        <v>22.03331658222185</v>
+        <v>9633</v>
       </c>
       <c r="F46" t="n">
-        <v>1.323424371734479</v>
+        <v>140.3571424978056</v>
       </c>
       <c r="G46" t="n">
-        <v>0.004456070652549234</v>
+        <v>1.0661010129152</v>
       </c>
       <c r="H46" t="n">
-        <v>0.000267652510766935</v>
+        <v>0.01456981942842473</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8390615718246441</v>
+        <v>0.0001106669669545177</v>
       </c>
       <c r="J46" t="n">
-        <v>0.07752962255165763</v>
+        <v>1.089097519962841</v>
       </c>
       <c r="K46" t="n">
-        <v>9.804808541461031e-05</v>
+        <v>0.007858314222222782</v>
       </c>
       <c r="L46" t="n">
-        <v>0.01399092970521542</v>
+        <v>3.958742815723861e-05</v>
       </c>
       <c r="M46" t="n">
-        <v>69.17901611328125</v>
+        <v>0.03700680272108844</v>
+      </c>
+      <c r="N46" t="n">
+        <v>356.501953125</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Owl</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>owl_TAG4learSOAEwf1.mat</t>
+          <t>ALrearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>5768.206787109375</v>
+        <v>2804.69970703125</v>
       </c>
       <c r="E47" t="n">
-        <v>53.45315335308301</v>
+        <v>2805</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9190683849990305</v>
+        <v>176.1655999151533</v>
       </c>
       <c r="G47" t="n">
-        <v>0.00926685802467044</v>
+        <v>1.477396248695336</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0001593334668675434</v>
+        <v>0.06281085974142418</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8631836995948721</v>
+        <v>0.0005267573726312207</v>
       </c>
       <c r="J47" t="n">
-        <v>0.01707213762777284</v>
+        <v>0.3729819684703501</v>
       </c>
       <c r="K47" t="n">
-        <v>5.101002314508482e-05</v>
+        <v>0.002414868145367197</v>
       </c>
       <c r="L47" t="n">
-        <v>0.02600907029478458</v>
+        <v>4.42198532442186e-05</v>
       </c>
       <c r="M47" t="n">
-        <v>150.0256958007812</v>
+        <v>0.1580045351473923</v>
+      </c>
+      <c r="N47" t="n">
+        <v>443.1552734375</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Owl</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>owl_TAG4learSOAEwf1.mat</t>
+          <t>ALrearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>7184.014892578125</v>
+        <v>2941.973876953125</v>
       </c>
       <c r="E48" t="n">
-        <v>212.2932172223761</v>
+        <v>2942</v>
       </c>
       <c r="F48" t="n">
-        <v>2.814804876179097</v>
+        <v>231.3411397684391</v>
       </c>
       <c r="G48" t="n">
-        <v>0.02955077632727324</v>
+        <v>0.9827744244215141</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0003918150112811012</v>
+        <v>0.07863466823438593</v>
       </c>
       <c r="I48" t="n">
-        <v>1.191974460537603</v>
+        <v>0.0003340527365386844</v>
       </c>
       <c r="J48" t="n">
-        <v>0.01450831463645014</v>
+        <v>0.577766738437872</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0002984796442141717</v>
+        <v>0.001945950411869513</v>
       </c>
       <c r="L48" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.097936446307927e-05</v>
       </c>
       <c r="M48" t="n">
-        <v>502.8810424804688</v>
+        <v>0.1929931972789116</v>
+      </c>
+      <c r="N48" t="n">
+        <v>567.7809448242188</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Owl</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>owl_TAG4learSOAEwf1.mat</t>
+          <t>ALrearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>9633.416748046875</v>
+        <v>3862.518310546875</v>
       </c>
       <c r="E49" t="n">
-        <v>140.3571424978056</v>
+        <v>3863</v>
       </c>
       <c r="F49" t="n">
-        <v>1.0661010129152</v>
+        <v>362.637066057466</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01456981942842473</v>
+        <v>1.46627892690428</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0001106669669545177</v>
+        <v>0.09388617396770917</v>
       </c>
       <c r="I49" t="n">
-        <v>1.089097519962841</v>
+        <v>0.0003796173400396583</v>
       </c>
       <c r="J49" t="n">
-        <v>0.007858314222222782</v>
+        <v>0.6294034046123487</v>
       </c>
       <c r="K49" t="n">
-        <v>3.958742815723861e-05</v>
+        <v>0.002148262592889671</v>
       </c>
       <c r="L49" t="n">
-        <v>0.03700680272108844</v>
+        <v>3.654524962554224e-05</v>
       </c>
       <c r="M49" t="n">
-        <v>356.501953125</v>
+        <v>0.2419954648526077</v>
+      </c>
+      <c r="N49" t="n">
+        <v>934.7119140625</v>
       </c>
     </row>
     <row r="50">
@@ -2662,42 +2811,45 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ALrearSOAEwf1.mat</t>
+          <t>JIrearSOAEwf2.mat</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2662.042236328125</v>
+        <v>2339.044189453125</v>
       </c>
       <c r="E50" t="n">
-        <v>154.5683002367715</v>
+        <v>2339</v>
       </c>
       <c r="F50" t="n">
-        <v>20.2478078044231</v>
+        <v>818.0269830360901</v>
       </c>
       <c r="G50" t="n">
-        <v>0.05806380459611887</v>
+        <v>2.853086902458008</v>
       </c>
       <c r="H50" t="n">
-        <v>0.007606118163005488</v>
+        <v>0.3497270324026444</v>
       </c>
       <c r="I50" t="n">
-        <v>0.05730361108584175</v>
+        <v>0.001219766140085223</v>
       </c>
       <c r="J50" t="n">
-        <v>0.008330908507563151</v>
+        <v>1.11757968458436</v>
       </c>
       <c r="K50" t="n">
-        <v>3.068923439967621e-05</v>
+        <v>0.003152006810475112</v>
       </c>
       <c r="L50" t="n">
-        <v>0.1080045351473923</v>
+        <v>0.00030134144280724</v>
       </c>
       <c r="M50" t="n">
-        <v>287.5126342773438</v>
+        <v>0.8039909297052155</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1880.5703125</v>
       </c>
     </row>
     <row r="51">
@@ -2707,42 +2859,45 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ALrearSOAEwf1.mat</t>
+          <t>JIrearSOAEwf2.mat</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2804.69970703125</v>
+        <v>4050.933837890625</v>
       </c>
       <c r="E51" t="n">
-        <v>176.1655999151533</v>
+        <v>4051</v>
       </c>
       <c r="F51" t="n">
-        <v>1.477396248695336</v>
+        <v>857.4657825290018</v>
       </c>
       <c r="G51" t="n">
-        <v>0.06281085974142418</v>
+        <v>2.485602486899685</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0005267573726312207</v>
+        <v>0.2116711397526788</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3729819684703501</v>
+        <v>0.000613587529781521</v>
       </c>
       <c r="J51" t="n">
-        <v>0.002414868145367197</v>
+        <v>0.7888661749257536</v>
       </c>
       <c r="K51" t="n">
-        <v>4.42198532442186e-05</v>
+        <v>0.001956184463742182</v>
       </c>
       <c r="L51" t="n">
-        <v>0.1580045351473923</v>
+        <v>6.14051980342609e-05</v>
       </c>
       <c r="M51" t="n">
-        <v>443.1552734375</v>
+        <v>0.5260090702947846</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2130.827941894531</v>
       </c>
     </row>
     <row r="52">
@@ -2752,42 +2907,45 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ALrearSOAEwf1.mat</t>
+          <t>JIrearSOAEwf2.mat</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2941.973876953125</v>
+        <v>5838.189697265625</v>
       </c>
       <c r="E52" t="n">
-        <v>231.3411397684391</v>
+        <v>5838</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9827744244215141</v>
+        <v>582.1672554969074</v>
       </c>
       <c r="G52" t="n">
-        <v>0.07863466823438593</v>
+        <v>1.928650485276508</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0003340527365386844</v>
+        <v>0.09971708452186323</v>
       </c>
       <c r="I52" t="n">
-        <v>0.577766738437872</v>
+        <v>0.0003303507740044506</v>
       </c>
       <c r="J52" t="n">
-        <v>0.001945950411869513</v>
+        <v>0.6281392062187325</v>
       </c>
       <c r="K52" t="n">
-        <v>3.097936446307927e-05</v>
+        <v>0.001721833788449371</v>
       </c>
       <c r="L52" t="n">
-        <v>0.1929931972789116</v>
+        <v>2.295573700064898e-05</v>
       </c>
       <c r="M52" t="n">
-        <v>567.7809448242188</v>
+        <v>0.23</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1342.783630371094</v>
       </c>
     </row>
     <row r="53">
@@ -2797,42 +2955,45 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ALrearSOAEwf1.mat</t>
+          <t>JIrearSOAEwf2.mat</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3862.518310546875</v>
+        <v>8309.124755859375</v>
       </c>
       <c r="E53" t="n">
-        <v>362.637066057466</v>
+        <v>8309</v>
       </c>
       <c r="F53" t="n">
-        <v>1.46627892690428</v>
+        <v>1477.387745215637</v>
       </c>
       <c r="G53" t="n">
-        <v>0.09388617396770917</v>
+        <v>6.873960001886568</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0003796173400396583</v>
+        <v>0.1778030525024699</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6294034046123487</v>
+        <v>0.0008272784684138041</v>
       </c>
       <c r="J53" t="n">
-        <v>0.002148262592889671</v>
+        <v>0.9929970405870511</v>
       </c>
       <c r="K53" t="n">
-        <v>3.654524962554224e-05</v>
+        <v>0.003581760153445885</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2419954648526077</v>
+        <v>0.0002835568290464586</v>
       </c>
       <c r="M53" t="n">
-        <v>934.7119140625</v>
+        <v>0.46</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3822.197387695312</v>
       </c>
     </row>
     <row r="54">
@@ -2842,42 +3003,45 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>JIrearSOAEwf2.mat</t>
+          <t>LSrearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2339.044189453125</v>
+        <v>732.12890625</v>
       </c>
       <c r="E54" t="n">
-        <v>818.0269830360901</v>
+        <v>732</v>
       </c>
       <c r="F54" t="n">
-        <v>2.853086902458008</v>
+        <v>459.9522820566954</v>
       </c>
       <c r="G54" t="n">
-        <v>0.3497270324026444</v>
+        <v>1.833859691104052</v>
       </c>
       <c r="H54" t="n">
-        <v>0.001219766140085223</v>
+        <v>0.6282394782260319</v>
       </c>
       <c r="I54" t="n">
-        <v>1.11757968458436</v>
+        <v>0.002504831697599773</v>
       </c>
       <c r="J54" t="n">
-        <v>0.003152006810475112</v>
+        <v>0.3325920858994204</v>
       </c>
       <c r="K54" t="n">
-        <v>0.00030134144280724</v>
+        <v>0.00089721344560609</v>
       </c>
       <c r="L54" t="n">
-        <v>0.8039909297052155</v>
+        <v>6.360217371298852e-05</v>
       </c>
       <c r="M54" t="n">
-        <v>1880.5703125</v>
+        <v>1.153990929705215</v>
+      </c>
+      <c r="N54" t="n">
+        <v>844.8701171874999</v>
       </c>
     </row>
     <row r="55">
@@ -2887,42 +3051,45 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>JIrearSOAEwf2.mat</t>
+          <t>LSrearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4050.933837890625</v>
+        <v>985.14404296875</v>
       </c>
       <c r="E55" t="n">
-        <v>857.4657825290018</v>
+        <v>985</v>
       </c>
       <c r="F55" t="n">
-        <v>2.485602486899685</v>
+        <v>725.3229302911859</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2116711397526788</v>
+        <v>4.158031890215665</v>
       </c>
       <c r="H55" t="n">
-        <v>0.000613587529781521</v>
+        <v>0.7362607889354045</v>
       </c>
       <c r="I55" t="n">
-        <v>0.7888661749257536</v>
+        <v>0.00422073494723204</v>
       </c>
       <c r="J55" t="n">
-        <v>0.001956184463742182</v>
+        <v>0.2817330377467866</v>
       </c>
       <c r="K55" t="n">
-        <v>6.14051980342609e-05</v>
+        <v>0.001052159777386118</v>
       </c>
       <c r="L55" t="n">
-        <v>0.5260090702947846</v>
+        <v>0.0001067423618239231</v>
       </c>
       <c r="M55" t="n">
-        <v>2130.827941894531</v>
+        <v>1.278004535147392</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1259.0185546875</v>
       </c>
     </row>
     <row r="56">
@@ -2932,42 +3099,45 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JIrearSOAEwf2.mat</t>
+          <t>LSrearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>5838.189697265625</v>
+        <v>1633.831787109375</v>
       </c>
       <c r="E56" t="n">
-        <v>582.1672554969074</v>
+        <v>1634</v>
       </c>
       <c r="F56" t="n">
-        <v>1.928650485276508</v>
+        <v>132.6479606441344</v>
       </c>
       <c r="G56" t="n">
-        <v>0.09971708452186323</v>
+        <v>2.397952889834018</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0003303507740044506</v>
+        <v>0.08118826043825432</v>
       </c>
       <c r="I56" t="n">
-        <v>0.6281392062187325</v>
+        <v>0.001467686519966997</v>
       </c>
       <c r="J56" t="n">
-        <v>0.001721833788449371</v>
+        <v>0.2356713255700598</v>
       </c>
       <c r="K56" t="n">
-        <v>2.295573700064898e-05</v>
+        <v>0.003648140428762795</v>
       </c>
       <c r="L56" t="n">
-        <v>0.23</v>
+        <v>5.311503633653583e-05</v>
       </c>
       <c r="M56" t="n">
-        <v>1342.783630371094</v>
+        <v>0.1639909297052154</v>
+      </c>
+      <c r="N56" t="n">
+        <v>267.93359375</v>
       </c>
     </row>
     <row r="57">
@@ -2977,42 +3147,45 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>JIrearSOAEwf2.mat</t>
+          <t>LSrearSOAEwf1.mat</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>8309.124755859375</v>
+        <v>2225.994873046875</v>
       </c>
       <c r="E57" t="n">
-        <v>1477.387745215637</v>
+        <v>2226</v>
       </c>
       <c r="F57" t="n">
-        <v>6.873960001886568</v>
+        <v>635.0515194628832</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1778030525024699</v>
+        <v>2.200678927856144</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0008272784684138041</v>
+        <v>0.2852888509099052</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9929970405870511</v>
+        <v>0.0009886271323005882</v>
       </c>
       <c r="J57" t="n">
-        <v>0.003581760153445885</v>
+        <v>0.5993593148611787</v>
       </c>
       <c r="K57" t="n">
-        <v>0.0002835568290464586</v>
+        <v>0.001782129090638084</v>
       </c>
       <c r="L57" t="n">
-        <v>0.46</v>
+        <v>7.449231236129309e-05</v>
       </c>
       <c r="M57" t="n">
-        <v>3822.197387695312</v>
+        <v>0.7580045351473923</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1687.314208984375</v>
       </c>
     </row>
     <row r="58">
@@ -3022,42 +3195,45 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LSrearSOAEwf1.mat</t>
+          <t>TH13RearwaveformSOAE.mat</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>732.12890625</v>
+        <v>904.39453125</v>
       </c>
       <c r="E58" t="n">
-        <v>459.9522820566954</v>
+        <v>904</v>
       </c>
       <c r="F58" t="n">
-        <v>1.833859691104052</v>
+        <v>340.3587083733262</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6282394782260319</v>
+        <v>1.498505288578434</v>
       </c>
       <c r="H58" t="n">
-        <v>0.002504831697599773</v>
+        <v>0.376338751079026</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3325920858994204</v>
+        <v>0.001656915468636558</v>
       </c>
       <c r="J58" t="n">
-        <v>0.00089721344560609</v>
+        <v>0.3643858199685247</v>
       </c>
       <c r="K58" t="n">
-        <v>6.360217371298852e-05</v>
+        <v>0.001256514906015341</v>
       </c>
       <c r="L58" t="n">
-        <v>1.153990929705215</v>
+        <v>4.898474055674456e-05</v>
       </c>
       <c r="M58" t="n">
-        <v>844.8701171874999</v>
+        <v>0.78</v>
+      </c>
+      <c r="N58" t="n">
+        <v>705.427734375</v>
       </c>
     </row>
     <row r="59">
@@ -3067,42 +3243,45 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LSrearSOAEwf1.mat</t>
+          <t>TH13RearwaveformSOAE.mat</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>985.14404296875</v>
+        <v>1520.782470703125</v>
       </c>
       <c r="E59" t="n">
-        <v>725.3229302911859</v>
+        <v>1521</v>
       </c>
       <c r="F59" t="n">
-        <v>4.158031890215665</v>
+        <v>705.7090477313448</v>
       </c>
       <c r="G59" t="n">
-        <v>0.7362607889354045</v>
+        <v>1.580235200716575</v>
       </c>
       <c r="H59" t="n">
-        <v>0.00422073494723204</v>
+        <v>0.4640433864318966</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2817330377467866</v>
+        <v>0.001039093513476627</v>
       </c>
       <c r="J59" t="n">
-        <v>0.001052159777386118</v>
+        <v>0.6237543272398417</v>
       </c>
       <c r="K59" t="n">
-        <v>0.0001067423618239231</v>
+        <v>0.001024927364701251</v>
       </c>
       <c r="L59" t="n">
-        <v>1.278004535147392</v>
+        <v>5.663826914073826e-05</v>
       </c>
       <c r="M59" t="n">
-        <v>1259.0185546875</v>
+        <v>0.98</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1490.366821289062</v>
       </c>
     </row>
     <row r="60">
@@ -3112,267 +3291,45 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LSrearSOAEwf1.mat</t>
+          <t>TH13RearwaveformSOAE.mat</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1633.831787109375</v>
+        <v>2037.579345703125</v>
       </c>
       <c r="E60" t="n">
-        <v>132.6479606441344</v>
+        <v>2038</v>
       </c>
       <c r="F60" t="n">
-        <v>2.397952889834018</v>
+        <v>396.1173615031738</v>
       </c>
       <c r="G60" t="n">
-        <v>0.08118826043825432</v>
+        <v>0.8672071431213023</v>
       </c>
       <c r="H60" t="n">
-        <v>0.001467686519966997</v>
+        <v>0.1944058582741877</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2356713255700598</v>
+        <v>0.00042560656346958</v>
       </c>
       <c r="J60" t="n">
-        <v>0.003648140428762795</v>
+        <v>0.8287606991370521</v>
       </c>
       <c r="K60" t="n">
-        <v>5.311503633653583e-05</v>
+        <v>0.001427733139109237</v>
       </c>
       <c r="L60" t="n">
-        <v>0.1639909297052154</v>
+        <v>3.884413126222548e-05</v>
       </c>
       <c r="M60" t="n">
-        <v>267.93359375</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>2</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>LSrearSOAEwf1.mat</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>2225.994873046875</v>
-      </c>
-      <c r="E61" t="n">
-        <v>635.0515194628832</v>
-      </c>
-      <c r="F61" t="n">
-        <v>2.200678927856144</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0.2852888509099052</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.0009886271323005882</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0.5993593148611787</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0.001782129090638084</v>
-      </c>
-      <c r="K61" t="n">
-        <v>7.449231236129309e-05</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0.7580045351473923</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1687.314208984375</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>3</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>TH13RearwaveformSOAE.mat</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>904.39453125</v>
-      </c>
-      <c r="E62" t="n">
-        <v>340.3587083733262</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1.498505288578434</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0.376338751079026</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.001656915468636558</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0.3643858199685247</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0.001256514906015341</v>
-      </c>
-      <c r="K62" t="n">
-        <v>4.898474055674456e-05</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="M62" t="n">
-        <v>705.427734375</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>3</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>TH13RearwaveformSOAE.mat</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>1520.782470703125</v>
-      </c>
-      <c r="E63" t="n">
-        <v>705.7090477313448</v>
-      </c>
-      <c r="F63" t="n">
-        <v>1.580235200716575</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0.4640433864318966</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.001039093513476627</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0.6237543272398417</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0.001024927364701251</v>
-      </c>
-      <c r="K63" t="n">
-        <v>5.663826914073826e-05</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="M63" t="n">
-        <v>1490.366821289062</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>3</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>TH13RearwaveformSOAE.mat</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>2037.579345703125</v>
-      </c>
-      <c r="E64" t="n">
-        <v>396.1173615031738</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.8672071431213023</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0.1944058582741877</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.00042560656346958</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0.8287606991370521</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0.001427733139109237</v>
-      </c>
-      <c r="K64" t="n">
-        <v>3.884413126222548e-05</v>
-      </c>
-      <c r="L64" t="n">
         <v>0.4470068027210884</v>
       </c>
-      <c r="M64" t="n">
+      <c r="N60" t="n">
         <v>910.8118286132812</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>3</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>TH13RearwaveformSOAE.mat</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>2694.342041015625</v>
-      </c>
-      <c r="E65" t="n">
-        <v>61.99256044990353</v>
-      </c>
-      <c r="F65" t="n">
-        <v>1.784414012888034</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0.02300842265243191</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.0006622819173379355</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0.3794241508584474</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0.01059162849031102</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0.0001324147717781738</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0.06800453514739228</v>
-      </c>
-      <c r="M65" t="n">
-        <v>183.2274780273437</v>
       </c>
     </row>
   </sheetData>
